--- a/DataTables/DetailText/剧情/015_02治疗成功.xlsx
+++ b/DataTables/DetailText/剧情/015_02治疗成功.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A81AFD3A-0E63-4172-AB27-6385607182AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C07671F1-CC74-43E1-A97D-1F6B709D0050}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="44">
   <si>
     <t>StoryID</t>
   </si>
@@ -182,7 +182,183 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>无妨，您和令尊医术高明</t>
+    <t>无妨，您和令尊医术高明，赈灾药材用的是什么方子想必心里有数。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>......</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>但我得提醒您一句，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>赈</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>灾</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>药</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>材朝廷很重</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>视</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>，不只是一两个州府的事，更不是你我能管的事。</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>先生医</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>术闻</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>名全省，在下十分</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>钦</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>佩，不要浪</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>费</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>了老天</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>给</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>您的才</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>华</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>。在下告辞。</t>
+    </r>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -190,7 +366,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -246,6 +422,13 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Noto Sans JP"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Microsoft YaHei"/>
       <family val="2"/>
       <charset val="134"/>
     </font>
@@ -819,7 +1002,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
@@ -985,37 +1168,61 @@
       <c r="A8" s="1">
         <v>7</v>
       </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="2"/>
+      <c r="B8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>8</v>
+      </c>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
+      <c r="H8" s="3" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>8</v>
       </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="2"/>
+      <c r="B9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
+      <c r="H9" s="3" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>9</v>
       </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="2"/>
+      <c r="B10" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>8</v>
+      </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
+      <c r="H10" s="3" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" s="3"/>
@@ -1027,6 +1234,46 @@
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
     </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A12" s="3"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A14" s="3"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A15" s="3"/>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
